--- a/docs/measurement-target-classification-review-2026-h2.xlsx
+++ b/docs/measurement-target-classification-review-2026-h2.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 검토" sheetId="1" r:id="R7145998774364b51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공정변경 확인" sheetId="2" r:id="Rd6d31034f8fb43e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" r:id="Ra4459eaf0e7847a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 검토" sheetId="1" r:id="R56648009a62841b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공정변경 확인" sheetId="2" r:id="R1d0fd979e3d64480"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" r:id="Rbce4ae0928ba4c24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="16">
+  <x:fonts count="18">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -109,8 +109,19 @@
       <x:color rgb="FF9C0006"/>
       <x:name val="맑은 고딕"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color rgb="FF375623"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF375623"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -142,8 +153,48 @@
         <x:fgColor rgb="FFFCE8E6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -231,11 +282,25 @@
         <x:color rgb="FFA6B7C8"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="96">
+  <x:cellXfs count="156">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -440,18 +505,166 @@
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="11">
+  <x:dxfs count="13">
     <x:dxf>
       <x:font>
         <x:b/>
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -462,7 +675,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -473,7 +686,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -484,7 +697,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -495,7 +708,7 @@
         <x:color rgb="FF9C6500"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -506,7 +719,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -517,7 +730,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -528,7 +741,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -539,7 +752,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -550,7 +763,29 @@
         <x:color rgb="FF9C6500"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -20021,16 +20256,16 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="D260" s="18" t="str">
-        <x:v>타기관 신규</x:v>
+        <x:v>기존업체</x:v>
       </x:c>
       <x:c r="E260" s="18" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F260" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G260" s="17" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—기존업체 확정</x:v>
       </x:c>
       <x:c r="H260" s="17" t="str">
         <x:v>공정 변경,타기관 신규</x:v>
@@ -20081,7 +20316,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X260" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 타기관 신규 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(기존업체)</x:v>
       </x:c>
     </x:row>
     <x:row r="261" ht="34" customHeight="1">
@@ -23209,10 +23444,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F303" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G303" s="17" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H303" s="17" t="str">
         <x:v>공정 변경,최초실시</x:v>
@@ -23263,7 +23498,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X303" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 최초실시 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="304" ht="34" customHeight="1">
@@ -23277,16 +23512,16 @@
         <x:v>46213</x:v>
       </x:c>
       <x:c r="D304" s="18" t="str">
-        <x:v>기존업체</x:v>
+        <x:v>최초실시</x:v>
       </x:c>
       <x:c r="E304" s="18" t="str">
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F304" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G304" s="17" t="str">
-        <x:v>2026 H2 정상 journal에 최초실시/타기관 신규 token 없음</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H304" s="17" t="str">
         <x:v>공정 변경</x:v>
@@ -23337,7 +23572,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X304" s="17" t="str">
-        <x:v>기존 최초실시 ↔ 최종 기존업체 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="305" ht="34" customHeight="1">
@@ -23431,10 +23666,10 @@
         <x:v>N</x:v>
       </x:c>
       <x:c r="F306" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G306" s="17" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H306" s="17" t="str">
         <x:v>최초실시</x:v>
@@ -23485,7 +23720,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X306" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 최초실시 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="307" ht="34" customHeight="1">
@@ -23508,7 +23743,7 @@
         <x:v>불필요</x:v>
       </x:c>
       <x:c r="G307" s="17" t="str">
-        <x:v>2026 H2 측정일지 없음; 사용자 확인 완료—최초실시 확정</x:v>
+        <x:v>별도 사용자 확정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H307" s="17" t="str">
         <x:v>-</x:v>
@@ -23559,7 +23794,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X307" s="17" t="str">
-        <x:v>측정일지 없음; 미확정—기본 기존업체 값 입력 금지; 사용자 확인 완료(최초실시); 측정예정일 미정</x:v>
+        <x:v>측정일지 없음; 미확정—기본 기존업체 값 입력 금지; 측정예정일 미정; 별도 사용자 확정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="308" ht="34" customHeight="1">
@@ -23727,10 +23962,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F310" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G310" s="17" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="H310" s="17" t="str">
         <x:v>공정 변경,타기관 신규</x:v>
@@ -23781,7 +24016,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X310" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 타기관 신규 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(타기관 신규)</x:v>
       </x:c>
     </x:row>
     <x:row r="311" ht="34" customHeight="1">
@@ -23875,10 +24110,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F312" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G312" s="17" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="H312" s="17" t="str">
         <x:v>공정 변경,타기관 신규</x:v>
@@ -23929,7 +24164,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X312" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 타기관 신규 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(타기관 신규)</x:v>
       </x:c>
     </x:row>
     <x:row r="313" ht="34" customHeight="1">
@@ -23949,10 +24184,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F313" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G313" s="17" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="H313" s="17" t="str">
         <x:v>공정 변경,타기관 신규</x:v>
@@ -24003,7 +24238,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X313" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 타기관 신규 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(타기관 신규)</x:v>
       </x:c>
     </x:row>
     <x:row r="314" ht="34" customHeight="1">
@@ -24171,10 +24406,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F316" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G316" s="17" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="H316" s="17" t="str">
         <x:v>공정 변경,타기관 신규,소음 85 이상</x:v>
@@ -24225,7 +24460,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X316" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 타기관 신규 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(타기관 신규)</x:v>
       </x:c>
     </x:row>
     <x:row r="317" ht="34" customHeight="1">
@@ -24245,10 +24480,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F317" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G317" s="17" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H317" s="17" t="str">
         <x:v>공정 변경,최초실시</x:v>
@@ -24299,7 +24534,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X317" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 최초실시 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="318" ht="34" customHeight="1">
@@ -24319,10 +24554,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F318" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G318" s="17" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H318" s="17" t="str">
         <x:v>최초실시,공정 변경</x:v>
@@ -24373,7 +24608,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X318" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 최초실시 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="319" ht="34" customHeight="1">
@@ -24396,7 +24631,7 @@
         <x:v>불필요</x:v>
       </x:c>
       <x:c r="G319" s="17" t="str">
-        <x:v>2026 H2 측정일지 없음; 사용자 확인 완료—최초실시 확정</x:v>
+        <x:v>별도 사용자 확정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H319" s="17" t="str">
         <x:v>-</x:v>
@@ -24447,7 +24682,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X319" s="17" t="str">
-        <x:v>측정일지 없음; 미확정—기본 기존업체 값 입력 금지; 사용자 확인 완료(최초실시); 측정예정일 미정</x:v>
+        <x:v>측정일지 없음; 미확정—기본 기존업체 값 입력 금지; 측정예정일 미정; 별도 사용자 확정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="320" ht="34" customHeight="1">
@@ -24470,7 +24705,7 @@
         <x:v>불필요</x:v>
       </x:c>
       <x:c r="G320" s="17" t="str">
-        <x:v>2026 H2 측정일지 없음; 사용자 확인 완료—최초실시 확정</x:v>
+        <x:v>별도 사용자 확정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H320" s="17" t="str">
         <x:v>-</x:v>
@@ -24521,7 +24756,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X320" s="17" t="str">
-        <x:v>측정일지 없음; 미확정—기본 기존업체 값 입력 금지; 사용자 확인 완료(최초실시); 측정예정일 미정</x:v>
+        <x:v>측정일지 없음; 미확정—기본 기존업체 값 입력 금지; 측정예정일 미정; 별도 사용자 확정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="321" ht="34" customHeight="1">
@@ -24541,10 +24776,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F321" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G321" s="17" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H321" s="17" t="str">
         <x:v>최초실시,공정 변경</x:v>
@@ -24595,7 +24830,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X321" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 최초실시 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="322" ht="34" customHeight="1">
@@ -24615,10 +24850,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F322" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G322" s="17" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="H322" s="17" t="str">
         <x:v>공정 변경,타기관 신규</x:v>
@@ -24669,7 +24904,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X322" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 타기관 신규 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(타기관 신규)</x:v>
       </x:c>
     </x:row>
     <x:row r="323" ht="34" customHeight="1">
@@ -24689,10 +24924,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F323" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G323" s="17" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H323" s="17" t="str">
         <x:v>최초실시,공정 변경</x:v>
@@ -24743,7 +24978,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X323" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 최초실시 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="324" ht="34" customHeight="1">
@@ -24763,10 +24998,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F324" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G324" s="17" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H324" s="17" t="str">
         <x:v>최초실시,공정 변경</x:v>
@@ -24817,7 +25052,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X324" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 최초실시 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="325" ht="34" customHeight="1">
@@ -24837,10 +25072,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F325" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G325" s="17" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="H325" s="17" t="str">
         <x:v>공정 변경,타기관 신규</x:v>
@@ -24891,7 +25126,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X325" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 타기관 신규 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(타기관 신규)</x:v>
       </x:c>
     </x:row>
     <x:row r="326" ht="34" customHeight="1">
@@ -24911,10 +25146,10 @@
         <x:v>N</x:v>
       </x:c>
       <x:c r="F326" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G326" s="17" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H326" s="17" t="str">
         <x:v>최초실시,고시물질</x:v>
@@ -24965,7 +25200,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X326" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 최초실시 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="327" ht="34" customHeight="1">
@@ -24988,7 +25223,7 @@
         <x:v>불필요</x:v>
       </x:c>
       <x:c r="G327" s="17" t="str">
-        <x:v>2026 H2 최신 note 없음/공란; 사용자 확인 완료—최초실시 확정</x:v>
+        <x:v>별도 사용자 확정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H327" s="17" t="str">
         <x:v>-</x:v>
@@ -25039,7 +25274,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X327" s="17" t="str">
-        <x:v>note 공란; 미확정—기본 기존업체 값 입력 금지; 사용자 확인 완료(최초실시)</x:v>
+        <x:v>note 공란; 미확정—기본 기존업체 값 입력 금지; 별도 사용자 확정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="328" ht="34" customHeight="1">
@@ -25059,10 +25294,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F328" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G328" s="17" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H328" s="17" t="str">
         <x:v>최초실시,공정 변경</x:v>
@@ -25113,7 +25348,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X328" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 최초실시 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="329" ht="34" customHeight="1">
@@ -25133,10 +25368,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="F329" s="18" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="G329" s="17" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H329" s="17" t="str">
         <x:v>최초실시,공정 변경</x:v>
@@ -25187,7 +25422,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X329" s="17" t="str">
-        <x:v>기존 기존업체 ↔ 최종 최초실시 충돌</x:v>
+        <x:v>사용자 직접 수정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="330" ht="34" customHeight="1">
@@ -25210,7 +25445,7 @@
         <x:v>불필요</x:v>
       </x:c>
       <x:c r="G330" s="17" t="str">
-        <x:v>2026 H2 측정일지 없음; 사용자 확인 완료—최초실시 확정</x:v>
+        <x:v>별도 사용자 확정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H330" s="17" t="str">
         <x:v>-</x:v>
@@ -25261,7 +25496,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X330" s="17" t="str">
-        <x:v>측정일지 없음; 미확정—기본 기존업체 값 입력 금지; 사용자 확인 완료(최초실시)</x:v>
+        <x:v>측정일지 없음; 미확정—기본 기존업체 값 입력 금지; 별도 사용자 확정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
     <x:row r="331" ht="34" customHeight="1">
@@ -25284,7 +25519,7 @@
         <x:v>불필요</x:v>
       </x:c>
       <x:c r="G331" s="17" t="str">
-        <x:v>2026 H2 측정일지 없음; 사용자 확인 완료—최초실시 확정</x:v>
+        <x:v>별도 사용자 확정—최초실시 확정</x:v>
       </x:c>
       <x:c r="H331" s="17" t="str">
         <x:v>-</x:v>
@@ -25335,7 +25570,7 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="X331" s="17" t="str">
-        <x:v>측정일지 없음; 미확정—기본 기존업체 값 입력 금지; 사용자 확인 완료(최초실시); 측정예정일 미정</x:v>
+        <x:v>측정일지 없음; 미확정—기본 기존업체 값 입력 금지; 측정예정일 미정; 별도 사용자 확정 완료(최초실시)</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -25364,7 +25599,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98a4a999efba4cbc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2567fd971fa4435"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27567,7 +27802,7 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="D63" s="38" t="str">
-        <x:v>타기관 신규</x:v>
+        <x:v>기존업체</x:v>
       </x:c>
       <x:c r="E63" s="37" t="str">
         <x:v>공정 변경,타기관 신규</x:v>
@@ -27579,10 +27814,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H63" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I63" s="37" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—기존업체 확정</x:v>
       </x:c>
       <x:c r="J63" s="38" t="str">
         <x:v>existing</x:v>
@@ -27719,10 +27954,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H67" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I67" s="37" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="J67" s="38" t="str">
         <x:v>existing</x:v>
@@ -27742,7 +27977,7 @@
         <x:v>46213</x:v>
       </x:c>
       <x:c r="D68" s="38" t="str">
-        <x:v>기존업체</x:v>
+        <x:v>최초실시</x:v>
       </x:c>
       <x:c r="E68" s="37" t="str">
         <x:v>공정 변경</x:v>
@@ -27754,10 +27989,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H68" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I68" s="37" t="str">
-        <x:v>2026 H2 정상 journal에 최초실시/타기관 신규 token 없음</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="J68" s="38" t="str">
         <x:v>general_new</x:v>
@@ -27824,10 +28059,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H70" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I70" s="37" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="J70" s="38" t="str">
         <x:v>existing</x:v>
@@ -27894,10 +28129,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H72" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I72" s="37" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="J72" s="38" t="str">
         <x:v>existing</x:v>
@@ -27929,10 +28164,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H73" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I73" s="37" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="J73" s="38" t="str">
         <x:v>existing</x:v>
@@ -27999,10 +28234,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H75" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I75" s="37" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="J75" s="38" t="str">
         <x:v>existing</x:v>
@@ -28034,10 +28269,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H76" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I76" s="37" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="J76" s="38" t="str">
         <x:v>existing</x:v>
@@ -28069,10 +28304,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H77" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I77" s="37" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="J77" s="38" t="str">
         <x:v>existing</x:v>
@@ -28104,10 +28339,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H78" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I78" s="37" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="J78" s="38" t="str">
         <x:v>existing</x:v>
@@ -28139,10 +28374,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H79" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I79" s="37" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="J79" s="38" t="str">
         <x:v>existing</x:v>
@@ -28174,10 +28409,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H80" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I80" s="37" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="J80" s="38" t="str">
         <x:v>existing</x:v>
@@ -28209,10 +28444,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H81" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I81" s="37" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="J81" s="38" t="str">
         <x:v>existing</x:v>
@@ -28244,10 +28479,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H82" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I82" s="37" t="str">
-        <x:v>2026 H2 최신 note의 타기관 신규 token 우선</x:v>
+        <x:v>사용자 직접 수정—타기관 신규 확정</x:v>
       </x:c>
       <x:c r="J82" s="38" t="str">
         <x:v>existing</x:v>
@@ -28279,10 +28514,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H83" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I83" s="37" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="J83" s="38" t="str">
         <x:v>existing</x:v>
@@ -28314,10 +28549,10 @@
         <x:v>공정 변경</x:v>
       </x:c>
       <x:c r="H84" s="38" t="str">
-        <x:v>필요</x:v>
+        <x:v>불필요</x:v>
       </x:c>
       <x:c r="I84" s="37" t="str">
-        <x:v>2026 H2 최신 note의 최초실시 token</x:v>
+        <x:v>사용자 직접 수정—최초실시 확정</x:v>
       </x:c>
       <x:c r="J84" s="38" t="str">
         <x:v>existing</x:v>
@@ -28352,7 +28587,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6811c0249634017"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab5b7b1447c24d6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28361,25 +28596,29 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="38" customHeight="1">
-      <x:c r="A1" s="44" t="str">
+      <x:c r="A1" s="130" t="str">
         <x:v>2026년 하반기 측정대상사업장 분류 최종 검토</x:v>
       </x:c>
-      <x:c r="B1" s="44"/>
-      <x:c r="C1" s="44"/>
-      <x:c r="D1" s="44"/>
-      <x:c r="E1" s="44"/>
-      <x:c r="F1" s="44"/>
-      <x:c r="G1" s="44"/>
+      <x:c r="B1" s="130"/>
+      <x:c r="C1" s="130"/>
+      <x:c r="D1" s="130"/>
+      <x:c r="E1" s="130"/>
+      <x:c r="F1" s="130"/>
+      <x:c r="G1" s="130"/>
+      <x:c r="H1" s="130"/>
+      <x:c r="I1" s="130"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="21"/>
@@ -28391,56 +28630,70 @@
       <x:c r="G2" s="21"/>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="131" t="str">
         <x:v>전체 대상</x:v>
       </x:c>
-      <x:c r="B3" s="34" t="str">
-        <x:v>기존업체</x:v>
-      </x:c>
-      <x:c r="C3" s="34" t="str">
+      <x:c r="B3" s="132" t="str">
+        <x:v>기존업체</x:v>
+      </x:c>
+      <x:c r="C3" s="132" t="str">
         <x:v>최초실시</x:v>
       </x:c>
-      <x:c r="D3" s="34" t="str">
+      <x:c r="D3" s="132" t="str">
         <x:v>타기관 신규</x:v>
       </x:c>
-      <x:c r="E3" s="34" t="str">
+      <x:c r="E3" s="132" t="str">
         <x:v>공정변경</x:v>
       </x:c>
-      <x:c r="F3" s="34" t="str">
+      <x:c r="F3" s="132" t="str">
         <x:v>측정예정일 미정</x:v>
       </x:c>
-      <x:c r="G3" s="35" t="str">
-        <x:v>사용자 확인 필요</x:v>
+      <x:c r="G3" s="133" t="str">
+        <x:v>기본유형 사용자 확인 필요</x:v>
+      </x:c>
+      <x:c r="H3" s="134" t="str">
+        <x:v>사용자 직접 검토 완료</x:v>
+      </x:c>
+      <x:c r="I3" s="134" t="str">
+        <x:v>별도 사용자 확정 최초실시</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="36" customHeight="1">
-      <x:c r="A4" s="82" t="n">
+      <x:c r="A4" s="140" t="n">
         <x:f>COUNTA('전체 검토'!$A$2:$A$331)</x:f>
         <x:v>330</x:v>
       </x:c>
-      <x:c r="B4" s="82" t="n">
+      <x:c r="B4" s="140" t="n">
         <x:f>COUNTIF('전체 검토'!$D$2:$D$331,"기존업체")</x:f>
         <x:v>302</x:v>
       </x:c>
-      <x:c r="C4" s="82" t="n">
+      <x:c r="C4" s="140" t="n">
         <x:f>COUNTIF('전체 검토'!$D$2:$D$331,"최초실시")</x:f>
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D4" s="82" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D4" s="140" t="n">
         <x:f>COUNTIF('전체 검토'!$D$2:$D$331,"타기관 신규")</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E4" s="82" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E4" s="140" t="n">
         <x:f>COUNTIF('전체 검토'!$E$2:$E$331,"Y")</x:f>
         <x:v>83</x:v>
       </x:c>
-      <x:c r="F4" s="83" t="n">
+      <x:c r="F4" s="145" t="n">
         <x:f>COUNTIF('전체 검토'!$C$2:$C$331,"미정")</x:f>
         <x:v>180</x:v>
       </x:c>
-      <x:c r="G4" s="84" t="n">
+      <x:c r="G4" s="148" t="n">
         <x:f>COUNTIF('전체 검토'!$F$2:$F$331,"필요")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H4" s="148" t="n">
+        <x:f>COUNTIF('요약'!$E$34:$E$57,"사용자 직접 수정")</x:f>
         <x:v>18</x:v>
+      </x:c>
+      <x:c r="I4" s="148" t="n">
+        <x:f>COUNTIF('요약'!$E$34:$E$57,"별도 사용자 확정")</x:f>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -28523,113 +28776,100 @@
       <x:c r="G11" s="21"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="93" t="str">
-        <x:v>사용자 확정 반영</x:v>
-      </x:c>
-      <x:c r="B12" s="95" t="str">
+      <x:c r="A12" s="154" t="str">
+        <x:v>사용자 검토 상태</x:v>
+      </x:c>
+      <x:c r="B12" s="154" t="str">
         <x:v>건수</x:v>
       </x:c>
-      <x:c r="C12" s="94" t="str">
+      <x:c r="C12" s="154" t="str">
         <x:v>결과</x:v>
       </x:c>
-      <x:c r="D12" s="21"/>
-      <x:c r="E12" s="21"/>
-      <x:c r="F12" s="21"/>
-      <x:c r="G12" s="21"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
-      <x:c r="A13" s="90" t="str">
-        <x:v>H0497 / H0509 / H0510
-H0518 / H0521 / H0523</x:v>
-      </x:c>
-      <x:c r="B13" s="90" t="n">
+      <x:c r="A13" s="155" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+      <x:c r="B13" s="155" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C13" s="155" t="str">
+        <x:v>최종 기본유형 확정 / 확인 불필요</x:v>
+      </x:c>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="155" t="str">
+        <x:v>별도 사용자 확정</x:v>
+      </x:c>
+      <x:c r="B14" s="155" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C13" s="90" t="str">
-        <x:v>최초실시 / 확인 불필요</x:v>
-      </x:c>
-      <x:c r="D13" s="21"/>
-      <x:c r="E13" s="21"/>
-      <x:c r="F13" s="21"/>
-      <x:c r="G13" s="21"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="21"/>
-      <x:c r="B14" s="21"/>
-      <x:c r="C14" s="21"/>
-      <x:c r="D14" s="21"/>
-      <x:c r="E14" s="21"/>
-      <x:c r="F14" s="21"/>
-      <x:c r="G14" s="21"/>
+      <x:c r="C14" s="155" t="str">
+        <x:v>최초실시 확정 / 확인 불필요</x:v>
+      </x:c>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="21"/>
-      <x:c r="B15" s="21"/>
-      <x:c r="C15" s="21"/>
-      <x:c r="D15" s="21"/>
-      <x:c r="E15" s="21"/>
-      <x:c r="F15" s="21"/>
-      <x:c r="G15" s="21"/>
+      <x:c r="A15" s="155" t="str">
+        <x:v>기본유형 확인 필요 잔여</x:v>
+      </x:c>
+      <x:c r="B15" s="155" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="155" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="93" t="str">
-        <x:v>사용자 확인 필요 사유</x:v>
-      </x:c>
-      <x:c r="B16" s="95" t="str">
-        <x:v>건수</x:v>
-      </x:c>
-      <x:c r="C16" s="94" t="str">
-        <x:v>설명</x:v>
-      </x:c>
-      <x:c r="D16" s="21"/>
-      <x:c r="E16" s="21"/>
-      <x:c r="F16" s="21"/>
-      <x:c r="G16" s="21"/>
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="91" t="str">
-        <x:v>기존업체 → 최초실시</x:v>
-      </x:c>
-      <x:c r="B17" s="91" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C17" s="91" t="str">
-        <x:v>현재 legacy 값과 최종 기본유형 불일치</x:v>
-      </x:c>
-      <x:c r="D17" s="21"/>
-      <x:c r="E17" s="21"/>
-      <x:c r="F17" s="21"/>
-      <x:c r="G17" s="21"/>
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="91" t="str">
-        <x:v>기존업체 → 타기관 신규</x:v>
-      </x:c>
-      <x:c r="B18" s="91" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C18" s="91" t="str">
-        <x:v>현재 legacy 값과 최종 기본유형 불일치</x:v>
-      </x:c>
-      <x:c r="D18" s="21"/>
-      <x:c r="E18" s="21"/>
-      <x:c r="F18" s="21"/>
-      <x:c r="G18" s="21"/>
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="91" t="str">
-        <x:v>최초실시 → 기존업체</x:v>
-      </x:c>
-      <x:c r="B19" s="91" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="91" t="str">
-        <x:v>현재 legacy 값과 최종 기본유형 불일치</x:v>
-      </x:c>
-      <x:c r="D19" s="21"/>
-      <x:c r="E19" s="21"/>
-      <x:c r="F19" s="21"/>
-      <x:c r="G19" s="21"/>
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="21"/>
@@ -28791,131 +29031,454 @@
       <x:c r="G32" s="21"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="93" t="str">
+      <x:c r="A33" s="139" t="str">
         <x:v>확정 코드</x:v>
       </x:c>
-      <x:c r="B33" s="95" t="str">
+      <x:c r="B33" s="139" t="str">
         <x:v>사업장명</x:v>
       </x:c>
-      <x:c r="C33" s="95" t="str">
+      <x:c r="C33" s="139" t="str">
         <x:v>측정예정일</x:v>
       </x:c>
-      <x:c r="D33" s="94" t="str">
+      <x:c r="D33" s="139" t="str">
         <x:v>최종 기본유형</x:v>
       </x:c>
-      <x:c r="E33" s="21"/>
-      <x:c r="F33" s="21"/>
-      <x:c r="G33" s="21"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="87" t="str">
+      <x:c r="E33" s="139" t="str">
+        <x:v>확정 구분</x:v>
+      </x:c>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+    </x:row>
+    <x:row r="34" ht="30" customHeight="1">
+      <x:c r="A34" s="108" t="str">
+        <x:v>H0439</x:v>
+      </x:c>
+      <x:c r="B34" s="90" t="str">
+        <x:v>입장모터스</x:v>
+      </x:c>
+      <x:c r="C34" s="109" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="D34" s="108" t="str">
+        <x:v>기존업체</x:v>
+      </x:c>
+      <x:c r="E34" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+    </x:row>
+    <x:row r="35" ht="30" customHeight="1">
+      <x:c r="A35" s="108" t="str">
+        <x:v>H0493</x:v>
+      </x:c>
+      <x:c r="B35" s="90" t="str">
+        <x:v>에스오토 서비스(S AUTO SERVICE)</x:v>
+      </x:c>
+      <x:c r="C35" s="109" t="n">
+        <x:v>46223</x:v>
+      </x:c>
+      <x:c r="D35" s="108" t="str">
+        <x:v>최초실시</x:v>
+      </x:c>
+      <x:c r="E35" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
+    </x:row>
+    <x:row r="36" ht="30" customHeight="1">
+      <x:c r="A36" s="108" t="str">
+        <x:v>H0494</x:v>
+      </x:c>
+      <x:c r="B36" s="90" t="str">
+        <x:v>(주) 다경종합건설 홍성군 25-A-00부대 시설공사</x:v>
+      </x:c>
+      <x:c r="C36" s="109" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="D36" s="108" t="str">
+        <x:v>최초실시</x:v>
+      </x:c>
+      <x:c r="E36" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+      <x:c r="F36"/>
+      <x:c r="G36"/>
+    </x:row>
+    <x:row r="37" ht="30" customHeight="1">
+      <x:c r="A37" s="108" t="str">
+        <x:v>H0496</x:v>
+      </x:c>
+      <x:c r="B37" s="90" t="str">
+        <x:v>주식회사 세진씰</x:v>
+      </x:c>
+      <x:c r="C37" s="109" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="D37" s="108" t="str">
+        <x:v>최초실시</x:v>
+      </x:c>
+      <x:c r="E37" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+    </x:row>
+    <x:row r="38" ht="30" customHeight="1">
+      <x:c r="A38" s="108" t="str">
         <x:v>H0497</x:v>
       </x:c>
-      <x:c r="B34" s="87" t="str">
+      <x:c r="B38" s="90" t="str">
         <x:v>주식회사 원팩</x:v>
       </x:c>
-      <x:c r="C34" s="92" t="str">
+      <x:c r="C38" s="109" t="str">
         <x:v>미정</x:v>
       </x:c>
-      <x:c r="D34" s="87" t="str">
+      <x:c r="D38" s="108" t="str">
         <x:v>최초실시</x:v>
       </x:c>
-      <x:c r="E34" s="21"/>
-      <x:c r="F34" s="21"/>
-      <x:c r="G34" s="21"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="87" t="str">
+      <x:c r="E38" s="108" t="str">
+        <x:v>별도 사용자 확정</x:v>
+      </x:c>
+      <x:c r="F38"/>
+      <x:c r="G38"/>
+    </x:row>
+    <x:row r="39" ht="30" customHeight="1">
+      <x:c r="A39" s="108" t="str">
+        <x:v>H0500</x:v>
+      </x:c>
+      <x:c r="B39" s="90" t="str">
+        <x:v>(주) 천안모터스</x:v>
+      </x:c>
+      <x:c r="C39" s="109" t="n">
+        <x:v>46223</x:v>
+      </x:c>
+      <x:c r="D39" s="108" t="str">
+        <x:v>타기관 신규</x:v>
+      </x:c>
+      <x:c r="E39" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+      <x:c r="F39"/>
+      <x:c r="G39"/>
+    </x:row>
+    <x:row r="40" ht="30" customHeight="1">
+      <x:c r="A40" s="108" t="str">
+        <x:v>H0502</x:v>
+      </x:c>
+      <x:c r="B40" s="90" t="str">
+        <x:v>제일모터스</x:v>
+      </x:c>
+      <x:c r="C40" s="109" t="n">
+        <x:v>46223</x:v>
+      </x:c>
+      <x:c r="D40" s="108" t="str">
+        <x:v>타기관 신규</x:v>
+      </x:c>
+      <x:c r="E40" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="30" customHeight="1">
+      <x:c r="A41" s="108" t="str">
+        <x:v>H0503</x:v>
+      </x:c>
+      <x:c r="B41" s="90" t="str">
+        <x:v>(주) 신방모터스</x:v>
+      </x:c>
+      <x:c r="C41" s="109" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="D41" s="108" t="str">
+        <x:v>타기관 신규</x:v>
+      </x:c>
+      <x:c r="E41" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="30" customHeight="1">
+      <x:c r="A42" s="108" t="str">
+        <x:v>H0506</x:v>
+      </x:c>
+      <x:c r="B42" s="90" t="str">
+        <x:v>탑모터스</x:v>
+      </x:c>
+      <x:c r="C42" s="109" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="D42" s="108" t="str">
+        <x:v>타기관 신규</x:v>
+      </x:c>
+      <x:c r="E42" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="30" customHeight="1">
+      <x:c r="A43" s="108" t="str">
+        <x:v>H0507</x:v>
+      </x:c>
+      <x:c r="B43" s="90" t="str">
+        <x:v>와이제이(YJ)모터스</x:v>
+      </x:c>
+      <x:c r="C43" s="109" t="n">
+        <x:v>46223</x:v>
+      </x:c>
+      <x:c r="D43" s="108" t="str">
+        <x:v>최초실시</x:v>
+      </x:c>
+      <x:c r="E43" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="30" customHeight="1">
+      <x:c r="A44" s="108" t="str">
+        <x:v>H0508</x:v>
+      </x:c>
+      <x:c r="B44" s="90" t="str">
+        <x:v>남영물류산업 (주) YAN5 Manless Mezzanine 공사</x:v>
+      </x:c>
+      <x:c r="C44" s="109" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="D44" s="108" t="str">
+        <x:v>최초실시</x:v>
+      </x:c>
+      <x:c r="E44" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="30" customHeight="1">
+      <x:c r="A45" s="108" t="str">
         <x:v>H0509</x:v>
       </x:c>
-      <x:c r="B35" s="87" t="str">
+      <x:c r="B45" s="90" t="str">
         <x:v>문화전기기업사 24-충-공-3 전기공사</x:v>
       </x:c>
-      <x:c r="C35" s="92" t="str">
+      <x:c r="C45" s="109" t="str">
         <x:v>미정</x:v>
       </x:c>
-      <x:c r="D35" s="87" t="str">
+      <x:c r="D45" s="108" t="str">
         <x:v>최초실시</x:v>
       </x:c>
-      <x:c r="E35" s="21"/>
-      <x:c r="F35" s="21"/>
-      <x:c r="G35" s="21"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="87" t="str">
+      <x:c r="E45" s="108" t="str">
+        <x:v>별도 사용자 확정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="30" customHeight="1">
+      <x:c r="A46" s="108" t="str">
         <x:v>H0510</x:v>
       </x:c>
-      <x:c r="B36" s="87" t="str">
+      <x:c r="B46" s="90" t="str">
         <x:v>주식회사 윤성워터텍 24-충-공-3 통신공사</x:v>
       </x:c>
-      <x:c r="C36" s="92" t="str">
+      <x:c r="C46" s="109" t="str">
         <x:v>미정</x:v>
       </x:c>
-      <x:c r="D36" s="87" t="str">
+      <x:c r="D46" s="108" t="str">
         <x:v>최초실시</x:v>
       </x:c>
-      <x:c r="E36" s="21"/>
-      <x:c r="F36" s="21"/>
-      <x:c r="G36" s="21"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="87" t="str">
+      <x:c r="E46" s="108" t="str">
+        <x:v>별도 사용자 확정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="30" customHeight="1">
+      <x:c r="A47" s="108" t="str">
+        <x:v>H0511</x:v>
+      </x:c>
+      <x:c r="B47" s="90" t="str">
+        <x:v>주식회사 에이치원건설 (주)테크윙 BIT사업장 기숙사, 접견동 신축공사</x:v>
+      </x:c>
+      <x:c r="C47" s="109" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="D47" s="108" t="str">
+        <x:v>최초실시</x:v>
+      </x:c>
+      <x:c r="E47" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="30" customHeight="1">
+      <x:c r="A48" s="108" t="str">
+        <x:v>H0512</x:v>
+      </x:c>
+      <x:c r="B48" s="90" t="str">
+        <x:v>합자회사 제일자동차정비공업사</x:v>
+      </x:c>
+      <x:c r="C48" s="109" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="D48" s="108" t="str">
+        <x:v>타기관 신규</x:v>
+      </x:c>
+      <x:c r="E48" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="30" customHeight="1">
+      <x:c r="A49" s="108" t="str">
+        <x:v>H0513</x:v>
+      </x:c>
+      <x:c r="B49" s="90" t="str">
+        <x:v>부영종합건설 주식회사 25-A-OO부대 시설공사(1349)</x:v>
+      </x:c>
+      <x:c r="C49" s="109" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="D49" s="108" t="str">
+        <x:v>최초실시</x:v>
+      </x:c>
+      <x:c r="E49" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="30" customHeight="1">
+      <x:c r="A50" s="108" t="str">
+        <x:v>H0514</x:v>
+      </x:c>
+      <x:c r="B50" s="90" t="str">
+        <x:v>주식회사 덕일건설 24-충-공-3 시설공사(보령)</x:v>
+      </x:c>
+      <x:c r="C50" s="109" t="n">
+        <x:v>46230</x:v>
+      </x:c>
+      <x:c r="D50" s="108" t="str">
+        <x:v>최초실시</x:v>
+      </x:c>
+      <x:c r="E50" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="30" customHeight="1">
+      <x:c r="A51" s="108" t="str">
+        <x:v>H0515</x:v>
+      </x:c>
+      <x:c r="B51" s="90" t="str">
+        <x:v>한국지엠남천안서비스센터 (주)</x:v>
+      </x:c>
+      <x:c r="C51" s="109" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="D51" s="108" t="str">
+        <x:v>타기관 신규</x:v>
+      </x:c>
+      <x:c r="E51" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="30" customHeight="1">
+      <x:c r="A52" s="108" t="str">
+        <x:v>H0516</x:v>
+      </x:c>
+      <x:c r="B52" s="90" t="str">
+        <x:v>(주)노디너리 천안공장</x:v>
+      </x:c>
+      <x:c r="C52" s="109" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="D52" s="108" t="str">
+        <x:v>최초실시</x:v>
+      </x:c>
+      <x:c r="E52" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="30" customHeight="1">
+      <x:c r="A53" s="108" t="str">
         <x:v>H0518</x:v>
       </x:c>
-      <x:c r="B37" s="87" t="str">
+      <x:c r="B53" s="90" t="str">
         <x:v>주식회사 명진전설 25-A-OO부대 소방공사(1348)</x:v>
       </x:c>
-      <x:c r="C37" s="92" t="n">
+      <x:c r="C53" s="109" t="n">
         <x:v>46241</x:v>
       </x:c>
-      <x:c r="D37" s="87" t="str">
+      <x:c r="D53" s="108" t="str">
         <x:v>최초실시</x:v>
       </x:c>
-      <x:c r="E37" s="21"/>
-      <x:c r="F37" s="21"/>
-      <x:c r="G37" s="21"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="87" t="str">
+      <x:c r="E53" s="108" t="str">
+        <x:v>별도 사용자 확정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="30" customHeight="1">
+      <x:c r="A54" s="108" t="str">
+        <x:v>H0519</x:v>
+      </x:c>
+      <x:c r="B54" s="90" t="str">
+        <x:v>하나전력 (주) 25-A-OO부대 전기공사(1346)</x:v>
+      </x:c>
+      <x:c r="C54" s="109" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="D54" s="108" t="str">
+        <x:v>최초실시</x:v>
+      </x:c>
+      <x:c r="E54" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="30" customHeight="1">
+      <x:c r="A55" s="108" t="str">
+        <x:v>H0520</x:v>
+      </x:c>
+      <x:c r="B55" s="90" t="str">
+        <x:v>(주) 태화전설 25-A-OO부대 통신공사(1347)</x:v>
+      </x:c>
+      <x:c r="C55" s="109" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="D55" s="108" t="str">
+        <x:v>최초실시</x:v>
+      </x:c>
+      <x:c r="E55" s="108" t="str">
+        <x:v>사용자 직접 수정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="30" customHeight="1">
+      <x:c r="A56" s="108" t="str">
         <x:v>H0521</x:v>
       </x:c>
-      <x:c r="B38" s="87" t="str">
+      <x:c r="B56" s="90" t="str">
         <x:v>서현자동차정비</x:v>
       </x:c>
-      <x:c r="C38" s="92" t="n">
+      <x:c r="C56" s="109" t="n">
         <x:v>46260</x:v>
       </x:c>
-      <x:c r="D38" s="87" t="str">
+      <x:c r="D56" s="108" t="str">
         <x:v>최초실시</x:v>
       </x:c>
-      <x:c r="E38" s="21"/>
-      <x:c r="F38" s="21"/>
-      <x:c r="G38" s="21"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="87" t="str">
+      <x:c r="E56" s="108" t="str">
+        <x:v>별도 사용자 확정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="30" customHeight="1">
+      <x:c r="A57" s="108" t="str">
         <x:v>H0523</x:v>
       </x:c>
-      <x:c r="B39" s="87" t="str">
+      <x:c r="B57" s="90" t="str">
         <x:v>지에스건설 (주) 가락상아1차아파트 재건축사업(서울)</x:v>
       </x:c>
-      <x:c r="C39" s="92" t="str">
+      <x:c r="C57" s="109" t="str">
         <x:v>미정</x:v>
       </x:c>
-      <x:c r="D39" s="87" t="str">
+      <x:c r="D57" s="108" t="str">
         <x:v>최초실시</x:v>
       </x:c>
-      <x:c r="E39" s="21"/>
-      <x:c r="F39" s="21"/>
-      <x:c r="G39" s="21"/>
+      <x:c r="E57" s="108" t="str">
+        <x:v>별도 사용자 확정</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A1:I1"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="C34:C39">
     <x:cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="미정"/>
   </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="C34:C57">
+    <x:cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="미정"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>